--- a/A-Documentacion/A-Inicio/Iteracion1-31_8-al-20_9/eGraduados_Inicio_Iteracion1_EstimacionPCU.xlsx
+++ b/A-Documentacion/A-Inicio/Iteracion1-31_8-al-20_9/eGraduados_Inicio_Iteracion1_EstimacionPCU.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\eGraduados\A-Documentacion\A-Inicio\Iteracion1-31_8-al-20_9\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF98BB25-001D-4483-BFCA-38E3DBE27A73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{641C61A4-A176-4823-BA01-D4A700B492F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -610,7 +610,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="121">
   <si>
     <t>ESTIMACIÓN por PUNTOS de CASO de USO</t>
   </si>
@@ -1065,9 +1065,6 @@
     <t>Inicio - Iteración 1</t>
   </si>
   <si>
-    <t>UARFDlow</t>
-  </si>
-  <si>
     <t>BBDD</t>
   </si>
   <si>
@@ -1081,6 +1078,15 @@
   </si>
   <si>
     <t>Framework UARGFlow para login de usuarios</t>
+  </si>
+  <si>
+    <t>UARGFlow</t>
+  </si>
+  <si>
+    <t>teamo</t>
+  </si>
+  <si>
+    <t>yomasmiamor</t>
   </si>
 </sst>
 </file>
@@ -1728,6 +1734,9 @@
     <xf numFmtId="9" fontId="14" fillId="12" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="4" fillId="11" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -1747,9 +1756,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="4" fillId="11" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2011,14 +2017,14 @@
     </row>
     <row r="2" spans="1:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="B2" s="86" t="s">
+      <c r="B2" s="87" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="82"/>
-      <c r="G2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="84"/>
       <c r="H2" s="5"/>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
@@ -2140,7 +2146,7 @@
       <c r="B6" s="66" t="s">
         <v>109</v>
       </c>
-      <c r="C6" s="90">
+      <c r="C6" s="81">
         <v>46281</v>
       </c>
       <c r="D6" s="67"/>
@@ -2268,13 +2274,13 @@
     <row r="10" spans="1:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C10" s="14" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E10" s="16">
         <f t="shared" ref="E10:E12" si="0">IF(C10="Simple",1,IF(C10="Intermedio",2,IF(C10="Complejo",3,"error")))</f>
@@ -2310,13 +2316,13 @@
     <row r="11" spans="1:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
       <c r="B11" s="13" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E11" s="16">
         <f t="shared" si="0"/>
@@ -2352,13 +2358,13 @@
     <row r="12" spans="1:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
       <c r="B12" s="13" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C12" s="14" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E12" s="16">
         <f t="shared" si="0"/>
@@ -2394,12 +2400,12 @@
     <row r="13" spans="1:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
       <c r="B13" s="18"/>
-      <c r="C13" s="81" t="s">
+      <c r="C13" s="82" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="82"/>
-      <c r="E13" s="82"/>
-      <c r="F13" s="83"/>
+      <c r="D13" s="83"/>
+      <c r="E13" s="83"/>
+      <c r="F13" s="84"/>
       <c r="G13" s="20">
         <f>SUM(G10:G12)</f>
         <v>6</v>
@@ -2454,8 +2460,12 @@
     </row>
     <row r="15" spans="1:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="23"/>
+      <c r="B15" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="C15" s="23" t="s">
+        <v>120</v>
+      </c>
       <c r="D15" s="23"/>
       <c r="E15" s="24"/>
       <c r="F15" s="10"/>
@@ -2747,11 +2757,11 @@
     <row r="23" spans="1:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="29"/>
-      <c r="C23" s="87" t="s">
+      <c r="C23" s="88" t="s">
         <v>27</v>
       </c>
-      <c r="D23" s="88"/>
-      <c r="E23" s="89"/>
+      <c r="D23" s="89"/>
+      <c r="E23" s="90"/>
       <c r="F23" s="30">
         <f>SUM(F17:F22)</f>
         <v>15</v>
@@ -2838,11 +2848,11 @@
         <v>28</v>
       </c>
       <c r="B26" s="31"/>
-      <c r="C26" s="81" t="s">
+      <c r="C26" s="82" t="s">
         <v>29</v>
       </c>
-      <c r="D26" s="82"/>
-      <c r="E26" s="83"/>
+      <c r="D26" s="83"/>
+      <c r="E26" s="84"/>
       <c r="F26" s="20">
         <f>G13+F23</f>
         <v>21</v>
@@ -3505,13 +3515,13 @@
     </row>
     <row r="43" spans="1:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1"/>
-      <c r="B43" s="81" t="s">
+      <c r="B43" s="82" t="s">
         <v>53</v>
       </c>
-      <c r="C43" s="82"/>
-      <c r="D43" s="82"/>
-      <c r="E43" s="82"/>
-      <c r="F43" s="83"/>
+      <c r="C43" s="83"/>
+      <c r="D43" s="83"/>
+      <c r="E43" s="83"/>
+      <c r="F43" s="84"/>
       <c r="G43" s="37">
         <f>SUM(G30:G42)</f>
         <v>45</v>
@@ -3538,13 +3548,13 @@
     </row>
     <row r="44" spans="1:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1"/>
-      <c r="B44" s="81" t="s">
+      <c r="B44" s="82" t="s">
         <v>54</v>
       </c>
-      <c r="C44" s="82"/>
-      <c r="D44" s="82"/>
-      <c r="E44" s="82"/>
-      <c r="F44" s="83"/>
+      <c r="C44" s="83"/>
+      <c r="D44" s="83"/>
+      <c r="E44" s="83"/>
+      <c r="F44" s="84"/>
       <c r="G44" s="30">
         <f>0.6+(0.01*G43)</f>
         <v>1.05</v>
@@ -4001,13 +4011,13 @@
     </row>
     <row r="56" spans="1:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="1"/>
-      <c r="B56" s="81" t="s">
+      <c r="B56" s="82" t="s">
         <v>73</v>
       </c>
-      <c r="C56" s="82"/>
-      <c r="D56" s="82"/>
-      <c r="E56" s="82"/>
-      <c r="F56" s="83"/>
+      <c r="C56" s="83"/>
+      <c r="D56" s="83"/>
+      <c r="E56" s="83"/>
+      <c r="F56" s="84"/>
       <c r="G56" s="11">
         <f>SUM(G48:G55)</f>
         <v>13.5</v>
@@ -4034,13 +4044,13 @@
     </row>
     <row r="57" spans="1:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1"/>
-      <c r="B57" s="81" t="s">
+      <c r="B57" s="82" t="s">
         <v>74</v>
       </c>
-      <c r="C57" s="82"/>
-      <c r="D57" s="82"/>
-      <c r="E57" s="82"/>
-      <c r="F57" s="83"/>
+      <c r="C57" s="83"/>
+      <c r="D57" s="83"/>
+      <c r="E57" s="83"/>
+      <c r="F57" s="84"/>
       <c r="G57" s="11">
         <f>1.4 + (-0.03*G56)</f>
         <v>0.99499999999999988</v>
@@ -4158,13 +4168,13 @@
       <c r="A61" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="B61" s="84" t="s">
+      <c r="B61" s="85" t="s">
         <v>77</v>
       </c>
-      <c r="C61" s="82"/>
-      <c r="D61" s="82"/>
-      <c r="E61" s="82"/>
-      <c r="F61" s="83"/>
+      <c r="C61" s="83"/>
+      <c r="D61" s="83"/>
+      <c r="E61" s="83"/>
+      <c r="F61" s="84"/>
       <c r="G61" s="44">
         <f>F26*G44*G57</f>
         <v>21.939749999999997</v>
@@ -4323,11 +4333,11 @@
     </row>
     <row r="66" spans="1:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="1"/>
-      <c r="B66" s="85" t="s">
+      <c r="B66" s="86" t="s">
         <v>83</v>
       </c>
-      <c r="C66" s="82"/>
-      <c r="D66" s="83"/>
+      <c r="C66" s="83"/>
+      <c r="D66" s="84"/>
       <c r="E66" s="3"/>
       <c r="F66" s="1"/>
       <c r="G66" s="1"/>
